--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
   </si>
 </sst>
 </file>
@@ -848,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -878,6 +887,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920240</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
@@ -509,19 +509,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -561,19 +561,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -626,16 +626,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.18000000000001</v>
+      </c>
+      <c r="H2">
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -649,16 +652,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -695,16 +701,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88.64</v>
+      </c>
+      <c r="H5">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -783,10 +792,10 @@
         <v>27</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>26</v>
@@ -795,7 +804,7 @@
         <v>96.3</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -835,19 +844,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
@@ -76,13 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
   </si>
 </sst>
 </file>
@@ -535,19 +535,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>89.19</v>
+        <v>91.89</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -678,16 +678,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -701,19 +704,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -818,10 +821,10 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -830,7 +833,7 @@
         <v>89.19</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -898,7 +901,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>

--- a/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
+++ b/docentes/Morales Vallejo Jorge Luis - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
   </si>
 </sst>
 </file>
@@ -535,16 +526,16 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -626,19 +617,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,19 +643,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>96.3</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,19 +669,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>86.48999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,16 +695,16 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -798,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,16 +812,16 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -869,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,29 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920235</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
